--- a/sample_data/2_Alternate_Header_Format.xlsx
+++ b/sample_data/2_Alternate_Header_Format.xlsx
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301-111-222-000</t>
+          <t>999-200-100-000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shepherd's Voice Media</t>
+          <t>[TEST] Shepherd's Voice Media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,12 +491,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>302-222-333-000</t>
+          <t>999-200-200-000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pillar Construction Group</t>
+          <t>[TEST] Pillar Construction Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -526,12 +526,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>303-333-444-000</t>
+          <t>999-200-300-000</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Water Bottling Co.</t>
+          <t>[TEST] Living Water Bottling Co.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,12 +561,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>304-444-555-000</t>
+          <t>999-200-400-000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anchor Legal Services</t>
+          <t>[TEST] Anchor Legal Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -596,12 +596,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>305-555-666-000</t>
+          <t>999-200-500-000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Harvest Print &amp; Design</t>
+          <t>[TEST] Harvest Print &amp; Design</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
